--- a/artfynd/A 51697-2024 artfynd.xlsx
+++ b/artfynd/A 51697-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3547,7 +3547,7 @@
         <v>118539914</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>121197070</v>
       </c>
       <c r="B33" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4469,6 +4469,255 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121403005</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98102</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Stormyrberget, Nordingrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>669250</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6984006</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121406951</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79711</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Stormyrberget, Nordingrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>669235</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6984036</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-08-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erik Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
